--- a/clean/economics/china_coastal_listings_validated_2026-10-14.xlsx
+++ b/clean/economics/china_coastal_listings_validated_2026-10-14.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -521,42 +521,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>广州/深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sun Yat-sen University</t>
+          <t>Guangdong University of Finance and Economics</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>岭南学院</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>加入岭南·成就卓越 | 中山大学岭南学院全球招聘（教师+博士后）</t>
+          <t>“百万英才汇南粤”广东财经大学2026年博士后招聘公告</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>See announcement; rolling</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://lingnan.sysu.edu.cn/article/2580</t>
+          <t>http://rsc.gdufe.edu.cn/2026/0306/c4710a233784/page.htm</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -573,37 +573,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sun Yat-sen University</t>
+          <t>Guangdong University of Finance and Economics</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>岭南学院/中观经济学研究院</t>
+          <t>大学人事处（含经济学博士后）</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>中山大学中观经济学研究院公开招聘博士后</t>
+          <t>广东财经大学2026年招聘博士后（经济学/管理学/法学等）</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>长期有效; CV to sunyxi@mail.sysu.edu.cn</t>
+          <t>常年诚聘; 含经济学</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://lingnan.sysu.edu.cn/article/2774</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>sunyxi@mail.sysu.edu.cn</t>
+          <t>http://rsc.gdufe.edu.cn/2026/0429/c4948a238378/page.htm</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -625,42 +620,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jinan University</t>
+          <t>Guangdong University of Finance and Economics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>经济与社会研究院</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>暨南大学冯帅章教授团队招聘博士后</t>
+          <t>广东财经大学面向海内外招聘学科方向带头人的公告</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>材料发 iesr@jnu.edu.cn</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://iesr.jnu.edu.cn/2025/0624/c17209a839104/page.htm</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>iesr@jnu.edu.cn</t>
+          <t>http://rsc.gdufe.edu.cn/2025/0116/c12800a215856/page.htm</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -677,32 +667,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Guangdong University of Finance and Economics</t>
+          <t>Guangdong University of Foreign Studies</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>大学人事处（含经济学博士后）</t>
+          <t>人事处/人才招聘</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>广东财经大学2026年招聘博士后（经济学/管理学/法学等）</t>
+          <t>广东外语外贸大学2026年招聘师资博士后研究...</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>常年诚聘; 含经济学</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>http://rsc.gdufe.edu.cn/2026/0429/c4948a238378/page.htm</t>
+          <t>https://rsc.gdufs.edu.cn/info/1083/12549.htm</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -719,42 +709,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sun Yat-sen University</t>
+          <t>Guangdong University of Foreign Studies</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>国际金融学院</t>
+          <t>人事处/人才招聘</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>中山大学国际金融学院诚聘海内外英才（教师+博士后）</t>
+          <t>广东外语外贸大学应用经济学博士后科研流动站2024年科研博士后研究人员招聘简章</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>常年有效; 应用经济学等</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://isbf.sysu.edu.cn/zh-hans/article/2827</t>
+          <t>https://rsc.gdufs.edu.cn/info/1083/11977.htm</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -771,42 +761,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jinan University</t>
+          <t>Guangdong University of Foreign Studies</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>经济学院</t>
+          <t>人事处/人才招聘</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>暨南大学经济学院2025年诚聘海内外英才（含教师各层次与博士后）</t>
+          <t>广东外语外贸大学应用经济学博士后科研流动站2025年科研博士后研究人员招聘简章</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>材料发 ojjy@jnu.edu.cn</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://ec.jnu.edu.cn/2024/1129/c42192a826585/page.htm</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ojjy@jnu.edu.cn</t>
+          <t>https://rsc.gdufs.edu.cn/info/1083/12041.htm</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -823,32 +808,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jinan University</t>
+          <t>Guangdong University of Foreign Studies</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>大学博士后流动站（含理论/应用经济学）</t>
+          <t>人事处/人才招聘</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>暨南大学2026年博士后全球招聘（含应用经济学、理论经济学）</t>
+          <t>广东外语外贸大学应用经济学博士后科研流动站2026年科研博士后研究人员招聘简章</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>全年常态化接收</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HR/导师</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://hrdam.jnu.edu.cn/2026/0413/c343a853500/page.htm</t>
+          <t>https://rsc.gdufs.edu.cn/info/1083/12519.htm</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -870,37 +855,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South China Normal University</t>
+          <t>Guangdong University of Foreign Studies</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>经济与管理学院</t>
+          <t>人力资源部/经济贸易学院等</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>华南师范大学经济与管理学院博士后流动站常年招收（理论/应用经济学）</t>
+          <t>广外2026年招聘师资博士后（含应用经济学、金融学）</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>scnujgzp@126.com; 常年招收</t>
+          <t>常年接受师资博士后申请</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR/学院</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>http://em.scnu.edu.cn/xueshukeyan/boshihouliudongzhan/</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>scnujgzp@126.com</t>
+          <t>https://rsc.gdufs.edu.cn/info/1017/12559.htm</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -927,37 +907,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>应用经济学博士后流动站</t>
+          <t>经济贸易学院</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>广外应用经济学博士后科研流动站2026年科研博士后招聘简章</t>
+          <t>广外2026年面向海内外招聘人才（经贸学院含国贸/产业/数字经济等）</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>gpszk@gdufs.edu.cn; 常年接受</t>
+          <t>见公告各学院联系人</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>HR/导师</t>
+          <t>Email/学院</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://rsc.gdufs.edu.cn/info/1017/12909.htm</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>gpszk@gdufs.edu.cn</t>
+          <t>https://rsc.gdufs.edu.cn/info/1017/12399.htm</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -979,27 +954,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>人力资源部/经济贸易学院等</t>
+          <t>应用经济学博士后流动站</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>广外2026年招聘师资博士后（含应用经济学、金融学）</t>
+          <t>广外应用经济学博士后科研流动站2026年科研博士后招聘简章</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>常年接受师资博士后申请</t>
+          <t>gpszk@gdufs.edu.cn; 常年接受</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HR/学院</t>
+          <t>HR/导师</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://rsc.gdufs.edu.cn/info/1017/12559.htm</t>
+          <t>https://rsc.gdufs.edu.cn/info/1017/12909.htm</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>gpszk@gdufs.edu.cn</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1021,32 +1001,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Guangdong University of Foreign Studies</t>
+          <t>Guangdong University of Technology</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>经济贸易学院</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>广外2026年面向海内外招聘人才（经贸学院含国贸/产业/数字经济等）</t>
+          <t>广东工业大学经济学院高层次人才招聘（应用经济学/数字经济/金融等）</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>见公告各学院联系人</t>
+          <t>简历发学院人才专员邮箱</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Email/学院</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://rsc.gdufs.edu.cn/info/1017/12399.htm</t>
+          <t>https://jjxy.gdut.edu.cn/rczp/gccrc.htm</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1115,35 +1095,577 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Guangdong University of Technology</t>
+          <t>Jinan University</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>大学博士后流动站（含理论/应用经济学）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>暨南大学2026年博士后全球招聘（含应用经济学、理论经济学）</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>全年常态化接收</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>HR/导师</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://hrdam.jnu.edu.cn/2026/0413/c343a853500/page.htm</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Jinan University</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>经济与社会研究院</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>暨南大学冯帅章教授团队招聘博士后</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>材料发 iesr@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://iesr.jnu.edu.cn/2025/0624/c17209a839104/page.htm</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>iesr@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jinan University</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>广东工业大学经济学院高层次人才招聘（应用经济学/数字经济/金融等）</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>简历发学院人才专员邮箱</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>暨南大学经济学院2025年诚聘海内外英才（含教师各层次与博士后）</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>材料发 ojjy@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>https://jjxy.gdut.edu.cn/rczp/gccrc.htm</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.jnu.edu.cn/2024/1129/c42192a826585/page.htm</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ojjy@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>South China Normal University</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>华南师范大学经济与管理学院博士后流动站常年招收（理论/应用经济学）</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>scnujgzp@126.com; 常年招收</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>http://em.scnu.edu.cn/xueshukeyan/boshihouliudongzhan/</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>scnujgzp@126.com</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>人事处/人才招聘</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-09 中山大学区域国别研究院面向海内外招聘博士后启事</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://rcb.sysu.edu.cn/article/532</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>岭南学院/中观经济学研究院</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>中山大学中观经济学研究院公开招聘博士后</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>长期有效; CV to sunyxi@mail.sysu.edu.cn</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://lingnan.sysu.edu.cn/article/2774</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>sunyxi@mail.sysu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>国际金融学院</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>中山大学国际金融学院诚聘海内外英才（教师+博士后）</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>常年有效; 应用经济学等</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://isbf.sysu.edu.cn/zh-hans/article/2827</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>广州/深圳</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>岭南学院</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>中山大学岭南学院2026年招聘教师（含教研岗与博士后）</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CV to sunyxi@mail.sysu.edu.cn; rolling</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gaoxiaojob.com/announcement/detail/434822.html</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>sunyxi@mail.sysu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>广州/深圳</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>岭南学院</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>加入岭南·成就卓越 | 中山大学岭南学院全球招聘（教师+博士后）</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>See announcement; rolling</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://lingnan.sysu.edu.cn/article/2580</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Donghua University</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>旭日工商管理学院</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>东华大学旭日工商管理学院研究助理教授（RAP）招聘公告</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://glxy.dhu.edu.cn/2026/0520/c20103a376231/page.htm</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Donghua University</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>旭日工商管理学院</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东华大学旭日工商管理学院诚聘海内外英才</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://glxy.dhu.edu.cn/2024/1014/c20103a352033/page.htm</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Donghua University</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>旭日工商管理学院</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东华大学旭日工商管理学院诚聘海内外高层次人才</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://glxy.dhu.edu.cn/2026/0520/c20103a376232/page.htm</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>Academic</t>
         </is>
@@ -1177,6 +1699,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/clean/economics/china_coastal_listings_validated_2026-10-14.xlsx
+++ b/clean/economics/china_coastal_listings_validated_2026-10-14.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1668,6 +1668,1040 @@
       <c r="N25" t="inlineStr">
         <is>
           <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ECNU</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学经济与管理学院海内外诚聘英才</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.ecnu.edu.cn/02/ed/c42845a721645/page.htm</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ECUST</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>华东理工大学陈万思教授团队招聘博士后启事</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://bs.ecust.edu.cn/cms/ecust/szyky/szdw/zpqs.html</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ECUST</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>商学院教师岗位招聘启事</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://bs.ecust.edu.cn/cms/ecust/facultyAndResearch/teacherRecruit/0-000c77j842001.html</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ECUST</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>商学院管理科学与工程博士后科研流动站招聘启事</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://bs.ecust.edu.cn/cms/ecust/facultyAndResearch/teacherRecruit/450106463682564.html</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Fudan University</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>【2026年】复旦大学经济学院面向全球诚聘英才，热岑欢迎您的加盟</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://econ.fudan.edu.cn/info/1134/46327.htm</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>中银科技金融学院</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>上海交通大学中银科技金融学院诚聘天下英才</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97786.html</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/会计系</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>会计系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97769.html</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/信息技术与创新系</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>信息、技术与创新系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97772.html</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/数据与商务智能系</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>数据与商务智能系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97770.html</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>海外优青 | 欢迎依托上海交大安泰经济与管理学院申报</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/94461.html</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/管理科学系</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>管理科学系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97783.html</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/组织管理系</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>组织管理系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97785.html</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/经济系</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>经济系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97812.html</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/金融系</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>金融系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97771.html</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SUFE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026上海财经大学商学院世界经济与贸易系、产业经济系师资招聘</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://cob.sufe.edu.cn/Home/Detail/26953</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SUIBE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>国际组织学院</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>上海对外经贸大学国际组织学院（贸易谈判学院）2026年诚聘海内外英才</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.suibe.edu.cn/gjzz/2025/0421/c21874a183262/page.htm</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SUIBE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>人事处/人才招聘</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>上海对外经贸大学教学科研岗位人才招聘启事</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.suibe.edu.cn/rsc/2025/0401/c3652a182425/page.htm</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Shanghai University</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>上海大学经济学院2026年招聘1名数量经济学教师</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gaoxiaojob.com/announcement/detail/370987.html</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Shanghai University</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>经济学院数字经济与贸易教师岗位</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.shu.edu.cn/Ads/Ads?a=ff3d6c5d-27b3-4094-bb0c-f0ab7a5c945f</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ShanghaiTech</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>创业与管理学院</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>上海科技大学创业与管理学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.shanghaitech.edu.cn/2026/0922/c3517a1127559/page.htm</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tongji University</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Job Posting: Join Tongji SEM Prestigious Research Faculty</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.tongji.edu.cn/semch/56204.html</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tongji University</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>同济大学经济与管理学院应用经济博士后招聘</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>https://zp.tongji.edu.cn/info/1063/19717.htm</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1721,6 +2755,50 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/clean/economics/china_coastal_listings_validated_2026-10-14.xlsx
+++ b/clean/economics/china_coastal_listings_validated_2026-10-14.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="China Coastal Validated" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="China Coastal - Faculty + Postd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -521,42 +521,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Guangdong University of Finance and Economics</t>
+          <t>BFSU</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>经济学院</t>
+          <t>国际商学院</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>“百万英才汇南粤”广东财经大学2026年博士后招聘公告</t>
+          <t>北京外国语大学2026年教学科研岗位招聘公告</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>含国际商学院岗位</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>http://rsc.gdufe.edu.cn/2026/0306/c4710a233784/page.htm</t>
+          <t>https://www.bfsu.edu.cn/info/1062/23822.htm</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -568,27 +568,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Guangdong University of Finance and Economics</t>
+          <t>BFSU</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>大学人事处（含经济学博士后）</t>
+          <t>国际商学院</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>广东财经大学2026年招聘博士后（经济学/管理学/法学等）</t>
+          <t>北京外国语大学2026年第二批教学科研岗位招聘公告</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>常年诚聘; 含经济学</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -598,12 +598,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>http://rsc.gdufe.edu.cn/2026/0429/c4948a238378/page.htm</t>
+          <t>https://www.bfsu.edu.cn/info/1062/26262.htm</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -615,12 +615,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Guangdong University of Finance and Economics</t>
+          <t>BIT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>广东财经大学面向海内外招聘学科方向带头人的公告</t>
+          <t>【诚聘英才】北京理工大学经济学院专任教师及博士后招聘公告</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -645,12 +645,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>http://rsc.gdufe.edu.cn/2025/0116/c12800a215856/page.htm</t>
+          <t>https://soe.bit.edu.cn/lbt/b2d5331b505c49a3bc98591c4b90f43f.htm</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>nansu@bit.edu.cn</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -662,27 +667,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Guangdong University of Foreign Studies</t>
+          <t>BJTU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>人事处/人才招聘</t>
+          <t>经济管理学院</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>广东外语外贸大学2026年招聘师资博士后研究...</t>
+          <t>北京交通大学经济管理学院教师岗位招聘启事（常年有效）</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>常年有效；含思源博士后</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -692,12 +697,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://rsc.gdufs.edu.cn/info/1083/12549.htm</t>
+          <t>https://jingguan.bjtu.edu.cn/show-972-9001.html</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -709,42 +714,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Guangdong University of Foreign Studies</t>
+          <t>BJUT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>人事处/人才招聘</t>
+          <t>经济与管理学院</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>广东外语外贸大学应用经济学博士后科研流动站2024年科研博士后研究人员招聘简章</t>
+          <t>北京工业大学2026年公开招聘公告（第二批）</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>含师资博士后制度；经管学院岗位见附件</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://rsc.gdufs.edu.cn/info/1083/11977.htm</t>
+          <t>https://www.bjut.edu.cn/info/1072/9464.htm</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -756,27 +761,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Guangdong University of Foreign Studies</t>
+          <t>Beihang University</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>人事处/人才招聘</t>
+          <t>经济管理学院</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>广东外语外贸大学应用经济学博士后科研流动站2025年科研博士后研究人员招聘简章</t>
+          <t>北京航空航天大学经济管理学院2026年卓越百人博士后岗位招聘通知</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>含低碳经济、金融工程等方向</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -786,7 +791,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://rsc.gdufs.edu.cn/info/1083/12041.htm</t>
+          <t>http://boshihouzp.gaoxiaozp.com/gxbshzp/57840.html</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>skw@buaa.edu.cn</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -803,27 +813,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Guangdong University of Foreign Studies</t>
+          <t>Beihang University</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>人事处/人才招聘</t>
+          <t>经济管理学院</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>广东外语外贸大学应用经济学博士后科研流动站2026年科研博士后研究人员招聘简章</t>
+          <t>北航经管学院诚邀海内外优秀学者加盟！</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>含助理教授及博士后</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -833,12 +843,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://rsc.gdufs.edu.cn/info/1083/12519.htm</t>
+          <t>https://sem.buaa.edu.cn/info/1024/16832.htm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>skw@buaa.edu.cn</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -850,37 +865,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Guangdong University of Foreign Studies</t>
+          <t>Beijing Normal University</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>人力资源部/经济贸易学院等</t>
+          <t>经济与工商管理学院</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>广外2026年招聘师资博士后（含应用经济学、金融学）</t>
+          <t>北京师范大学经济与工商管理学院2026年招收博士后公告</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>常年接受师资博士后申请</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HR/学院</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://rsc.gdufs.edu.cn/info/1017/12559.htm</t>
+          <t>http://boshihoujob.com/gxbsh/beijing/133313.html</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -897,42 +912,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Guangdong University of Foreign Studies</t>
+          <t>Beijing Normal University</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>经济贸易学院</t>
+          <t>经济与工商管理学院</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>广外2026年面向海内外招聘人才（经贸学院含国贸/产业/数字经济等）</t>
+          <t>北京师范大学经济与工商管理学院2026年招收博士后公告（全球人才网）</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>见公告各学院联系人</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Email/学院</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://rsc.gdufs.edu.cn/info/1017/12399.htm</t>
+          <t>https://ifegg.com/html/12654.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -944,47 +959,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Guangdong University of Foreign Studies</t>
+          <t>Beijing Normal University</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>应用经济学博士后流动站</t>
+          <t>经济与工商管理学院</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>广外应用经济学博士后科研流动站2026年科研博士后招聘简章</t>
+          <t>北京师范大学经济与工商管理学院教学科研岗招聘启事（2026年）</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>gpszk@gdufs.edu.cn; 常年接受</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HR/导师</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://rsc.gdufs.edu.cn/info/1017/12909.htm</t>
+          <t>https://bs.bnu.edu.cn/bshzs/e8dc0779c4714d7b937e7a7634f44d20.html</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>gpszk@gdufs.edu.cn</t>
+          <t>bshr@bnu.edu.cn</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -996,37 +1011,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Guangdong University of Technology</t>
+          <t>Beijing Normal University</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>经济学院</t>
+          <t>经济与工商管理学院</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>广东工业大学经济学院高层次人才招聘（应用经济学/数字经济/金融等）</t>
+          <t>北师大经管学院教学科研岗位人才招聘启事（2026年）</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>简历发学院人才专员邮箱</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://jjxy.gdut.edu.cn/rczp/gccrc.htm</t>
+          <t>https://www.efnchina.com/info/1111/59261.htm</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bshr@bnu.edu.cn</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1043,42 +1063,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Guangzhou University</t>
+          <t>CAU</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>经济与统计学院</t>
+          <t>经济管理学院</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>广州大学经济与统计学院（李正辉课题组）2026年诚聘博士后</t>
+          <t>【诚聘】中国农业大学经济管理学院诚聘天下英才</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>金融统计与风险管理、宏观经济统计等</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.gaoxiaojob.com/announcement/detail/388060.html</t>
+          <t>https://cem.cau.edu.cn/art/2025/12/16/art_56853_1127416.html</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2017062@cau.edu.cn</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -1090,42 +1115,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jinan University</t>
+          <t>CAU</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>大学博士后流动站（含理论/应用经济学）</t>
+          <t>经济管理学院</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>暨南大学2026年博士后全球招聘（含应用经济学、理论经济学）</t>
+          <t>中国农业大学2026年度人才招聘启事</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>全年常态化接收</t>
+          <t>高层次/普通学术岗全年招聘</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>HR/导师</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://hrdam.jnu.edu.cn/2026/0413/c343a853500/page.htm</t>
+          <t>https://cau.edu.cn/tzgg/7080fc338ac04c4c87c78e37531fef46.htm</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -1137,47 +1162,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jinan University</t>
+          <t>CUC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>经济与社会研究院</t>
+          <t>经济与管理学院</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>暨南大学冯帅章教授团队招聘博士后</t>
+          <t>中国传媒大学2026年第二批教学科研岗公开招聘公告</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>材料发 iesr@jnu.edu.cn</t>
+          <t>含经济与管理学院教学科研岗</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://iesr.jnu.edu.cn/2025/0624/c17209a839104/page.htm</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>iesr@jnu.edu.cn</t>
+          <t>https://mkszyxy.cuc.edu.cn/2026/0603/c2346a271304/page.htm</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1209,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jinan University</t>
+          <t>CUEB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1204,27 +1224,22 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>暨南大学经济学院2025年诚聘海内外英才（含教师各层次与博士后）</t>
+          <t>首都经济贸易大学2026年公开招聘公告</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>材料发 ojjy@jnu.edu.cn</t>
+          <t>教学岗位含经济学院等</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://ec.jnu.edu.cn/2024/1129/c42192a826585/page.htm</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ojjy@jnu.edu.cn</t>
+          <t>https://rsj.beijing.gov.cn/xxgk/gkzp/202601/t20260130_4477634.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1241,47 +1256,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South China Normal University</t>
+          <t>CUEB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>经济与管理学院</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>华南师范大学经济与管理学院博士后流动站常年招收（理论/应用经济学）</t>
+          <t>首都经济贸易大学2026年公开招聘公告（第二批）</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>scnujgzp@126.com; 常年招收</t>
+          <t>教学岗位含经济学院等</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>http://em.scnu.edu.cn/xueshukeyan/boshihouliudongzhan/</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>scnujgzp@126.com</t>
+          <t>https://rsj.beijing.gov.cn/xxgk/gkzp/202606/t20260630_4740194.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1303,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sun Yat-sen University</t>
+          <t>CUFE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>人事处/人才招聘</t>
+          <t>经济学院/商学院</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2024-01-09 中山大学区域国别研究院面向海内外招聘博士后启事</t>
+          <t>中央财经大学2026年度人才招聘公告（第三批）</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1318,17 +1328,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://rcb.sysu.edu.cn/article/532</t>
+          <t>https://www.cufe.edu.cn/info/1186/26673.htm</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -1340,47 +1350,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sun Yat-sen University</t>
+          <t>CUFE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>岭南学院/中观经济学研究院</t>
+          <t>经济学院/商学院</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>中山大学中观经济学研究院公开招聘博士后</t>
+          <t>中央财经大学2026年度人才招聘公告（第二批）</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>长期有效; CV to sunyxi@mail.sysu.edu.cn</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://lingnan.sysu.edu.cn/article/2774</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>sunyxi@mail.sysu.edu.cn</t>
+          <t>https://www.cufe.edu.cn/info/1186/26420.htm</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -1392,37 +1397,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sun Yat-sen University</t>
+          <t>CUFE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>国际金融学院</t>
+          <t>经济学院/商学院</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>中山大学国际金融学院诚聘海内外英才（教师+博士后）</t>
+          <t>中央财经大学2026年度教学科研相关岗位人才招聘公告（第一批）</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>常年有效; 应用经济学等</t>
+          <t>含师资博士后通道</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://isbf.sysu.edu.cn/zh-hans/article/2827</t>
+          <t>https://hr.cufe.edu.cn/info/1046/3431.htm</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1439,47 +1444,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>广州/深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sun Yat-sen University</t>
+          <t>CUFE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>岭南学院</t>
+          <t>应用经济学/理论经济学/工商管理</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>中山大学岭南学院2026年招聘教师（含教研岗与博士后）</t>
+          <t>中央财经大学2026年度第一批博士后研究人员招收简章</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CV to sunyxi@mail.sysu.edu.cn; rolling</t>
+          <t>含应用经济学、理论经济学、工商管理流动站</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.gaoxiaojob.com/announcement/detail/434822.html</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>sunyxi@mail.sysu.edu.cn</t>
+          <t>https://postdoctor.cufe.edu.cn/info/1014/1396.htm</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1491,42 +1491,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>广州/深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sun Yat-sen University</t>
+          <t>CUFE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>岭南学院</t>
+          <t>应用经济学/理论经济学/工商管理</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>加入岭南·成就卓越 | 中山大学岭南学院全球招聘（教师+博士后）</t>
+          <t>中央财经大学2026年度第一批博士后研究人员招收简章（校官网）</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>See announcement; rolling</t>
+          <t>含应用经济学、理论经济学、工商管理</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://lingnan.sysu.edu.cn/article/2580</t>
+          <t>https://www.cufe.edu.cn/info/1186/26475.htm</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1538,22 +1538,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Donghua University</t>
+          <t>CUFE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>旭日工商管理学院</t>
+          <t>商学院</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东华大学旭日工商管理学院研究助理教授（RAP）招聘公告</t>
+          <t>中央财经大学商学院2026年度教学科研岗招聘公告</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://glxy.dhu.edu.cn/2026/0520/c20103a376231/page.htm</t>
+          <t>https://bs.cufe.edu.cn/info/1019/10469.htm</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1585,22 +1585,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Donghua University</t>
+          <t>CUFE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>旭日工商管理学院</t>
+          <t>商学院、科技商学院</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东华大学旭日工商管理学院诚聘海内外英才</t>
+          <t>中央财经大学商学院、科技商学院2026年度教学科研岗招聘公告（第三批）</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://glxy.dhu.edu.cn/2024/1014/c20103a352033/page.htm</t>
+          <t>http://bs.cufe.edu.cn/info/1019/11089.htm</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1632,22 +1632,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Donghua University</t>
+          <t>CUFE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>旭日工商管理学院</t>
+          <t>管理科学与工程学院</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东华大学旭日工商管理学院诚聘海内外高层次人才</t>
+          <t>中央财经大学管理科学与工程学院2026年度第一批龙马博士后研究人员招收简章</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://glxy.dhu.edu.cn/2026/0520/c20103a376232/page.htm</t>
+          <t>https://mse.cufe.edu.cn/info/1073/12521.htm</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1679,22 +1679,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ECNU</t>
+          <t>CUFE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>经济与管理学院</t>
+          <t>金融学院</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>华东师范大学经济与管理学院海内外诚聘英才</t>
+          <t>金融学院2026年度博士后研究人员招收简章</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://sem.ecnu.edu.cn/02/ed/c42845a721645/page.htm</t>
+          <t>https://sf.cufe.edu.cn/info/1104/15771.htm</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -1726,22 +1726,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ECUST</t>
+          <t>CUGB</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>商学院</t>
+          <t>经济管理学院</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>华东理工大学陈万思教授团队招聘博士后启事</t>
+          <t>中国地质大学（北京）2026年教师岗、实验员岗及专技岗位招聘启事（第二批）</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://bs.ecust.edu.cn/cms/ecust/szyky/szdw/zpqs.html</t>
+          <t>https://bm.cugb.edu.cn/rscnew/c/2026-04-30/849146.shtml</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -1773,27 +1773,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ECUST</t>
+          <t>CUP Beijing</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>商学院</t>
+          <t>经济管理学院</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>商学院教师岗位招聘启事</t>
+          <t>中国石油大学（北京）经济管理学院诚聘优秀人才</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>全年接受应聘，招满为止</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1803,7 +1803,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://bs.ecust.edu.cn/cms/ecust/facultyAndResearch/teacherRecruit/0-000c77j842001.html</t>
+          <t>https://www.cup.edu.cn/sba/rczp/a11fe97eb87141269783d3fded8c4456.htm</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>jgxy@cup.edu.cn</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -1820,37 +1825,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ECUST</t>
+          <t>Minzu University</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>商学院</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>商学院管理科学与工程博士后科研流动站招聘启事</t>
+          <t>中央民族大学2026年度博士后招收公告</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>普通博士后全年接受申请</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://bs.ecust.edu.cn/cms/ecust/facultyAndResearch/teacherRecruit/450106463682564.html</t>
+          <t>https://www.muc.edu.cn/info/1083/49048.htm</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -1867,22 +1872,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fudan University</t>
+          <t>NCEPU Baoding</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>经济学院</t>
+          <t>经济管理系</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>【2026年】复旦大学经济学院面向全球诚聘英才，热岑欢迎您的加盟</t>
+          <t>华北电力大学2026年度教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1897,7 +1902,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://econ.fudan.edu.cn/info/1134/46327.htm</t>
+          <t>https://www.ncepu.edu.cn/rczp/bjrczp/e5222acc770e4a7cb8e09eefad9098e1.htm</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -1914,22 +1919,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SJTU</t>
+          <t>NCEPU Baoding</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>中银科技金融学院</t>
+          <t>经济管理系</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>上海交通大学中银科技金融学院诚聘天下英才</t>
+          <t>华北电力大学2026年度教学科研岗位招聘启事（保定）</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1944,7 +1949,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97786.html</t>
+          <t>https://www.ncepu.edu.cn/rczp/bdrczp/c9e86b816a9e4c359d3bd2695f737a3a.htm</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -1961,22 +1966,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SJTU</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/会计系</t>
+          <t>光华管理学院</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>会计系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>2025年北京大学光华管理学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1991,7 +1996,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97769.html</t>
+          <t>https://hr.pku.edu.cn/rczp/jxky/a92f835c47714f1ababadf98678a5085.htm</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>recruitment@gsm.pku.edu.cn</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2008,22 +2018,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SJTU</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/信息技术与创新系</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>信息、技术与创新系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>2025年北京大学经济学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2038,7 +2048,12 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97772.html</t>
+          <t>https://hr.pku.edu.cn/rczp/jxky/f5471d5b1df745db9ff270ba2f4fc7db.htm</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>econ_pku_hr@163.com</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2055,22 +2070,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SJTU</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/数据与商务智能系</t>
+          <t>光华管理学院</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>数据与商务智能系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>2026年北京大学光华管理学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2085,7 +2100,12 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97770.html</t>
+          <t>https://hr.pku.edu.cn/rczp/jxky/5a8411beae2c4e8ba518ba4c6efe8794.htm</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>recruitment@gsm.pku.edu.cn</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2102,22 +2122,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SJTU</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>海外优青 | 欢迎依托上海交大安泰经济与管理学院申报</t>
+          <t>2026年北京大学经济学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2132,12 +2152,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/94461.html</t>
+          <t>https://hr.pku.edu.cn/rczp/jxky/aba345dfa9d040df8b64488f3af5b37a.htm</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>econ_pku_hr@163.com</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -2149,22 +2174,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SJTU</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/管理科学系</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>管理科学系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>北京大学经济学院2026年教职招聘通知</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2179,7 +2204,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97783.html</t>
+          <t>https://econ.pku.edu.cn/tzgg/50170econ391389.htm</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2196,27 +2221,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SJTU</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/组织管理系</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>组织管理系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>北京大学经济学院“奥园博士后”项目申请公告</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>全年滚动招收</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2226,12 +2251,12 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97785.html</t>
+          <t>https://econ.pku.edu.cn/tzgg/50170econ372315.htm</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -2243,22 +2268,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SJTU</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/经济系</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>经济系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>北京大学经济学院面向海内外诚聘英才</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2273,7 +2298,12 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97812.html</t>
+          <t>https://econ.pku.edu.cn/tzgg/334008.htm</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>econ_pku_hr@163.com</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2290,27 +2320,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SJTU</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/金融系</t>
+          <t>商学院</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>金融系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>中国人民大学商学院年度教师招聘（滚动至2026-12-31）</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>滚动招聘，招满即止</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2320,7 +2350,12 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97771.html</t>
+          <t>https://www.rmbs.ruc.edu.cn/szyky/rczp/ndjszp/97756c032dac49fab16e5a273f0ebf9d.htm</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>recruitment@rmbs.ruc.edu.cn</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2337,22 +2372,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SUFE</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>商学院</t>
+          <t>应用经济学院</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026上海财经大学商学院世界经济与贸易系、产业经济系师资招聘</t>
+          <t>中国人民大学应用经济学院博士后招聘公告</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2367,12 +2402,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://cob.sufe.edu.cn/Home/Detail/26953</t>
+          <t>http://ae.ruc.edu.cn/xwzx/tzgg/62a1d3280023497a9cc7a2c15c5894c7.htm</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -2384,27 +2419,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SUIBE</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>国际组织学院</t>
+          <t>财政金融学院</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>上海对外经贸大学国际组织学院（贸易谈判学院）2026年诚聘海内外英才</t>
+          <t>中国人民大学财政金融学院2026年度引进人才和教师通知</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>滚动招聘，招满即止</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2414,12 +2449,17 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.suibe.edu.cn/gjzz/2025/0421/c21874a183262/page.htm</t>
+          <t>https://ifegg.com/html/11188.html</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>cjzonghe@ruc.edu.cn</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -2431,37 +2471,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SUIBE</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>人事处/人才招聘</t>
+          <t>财政金融学院/经济学院</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>上海对外经贸大学教学科研岗位人才招聘启事</t>
+          <t>独树一帜走新路 汇聚英才谱新篇——关于中国人民大学2026年度人才引进和教师招聘通知</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>含财政金融学院、经济学院等</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://www.suibe.edu.cn/rsc/2025/0401/c3652a182425/page.htm</t>
+          <t>http://hr.ruc.edu.cn/zpxx/c26637043fc8457496f0781066bcad04.htm</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2478,27 +2518,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shanghai University</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>经济学院</t>
+          <t>财政金融学院</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>上海大学经济学院2026年招聘1名数量经济学教师</t>
+          <t>财政金融学院2026年度人才引进和教师招聘通知</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>滚动招聘，招满即止</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2508,12 +2548,17 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.gaoxiaojob.com/announcement/detail/370987.html</t>
+          <t>http://sf.ruc.edu.cn/sylm/gg_sy/gg/67fefa2748ef4125aa908c2f3bfed087.htm</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>cjzonghe@ruc.edu.cn</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -2525,27 +2570,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shanghai University</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>经济学院</t>
+          <t>经济管理学院</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>经济学院数字经济与贸易教师岗位</t>
+          <t>清华大学经济管理学院2026年招聘教研系列教师（经济系）</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>截止日期2026-12-31</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2555,12 +2600,12 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.shu.edu.cn/Ads/Ads?a=ff3d6c5d-27b3-4094-bb0c-f0ab7a5c945f</t>
+          <t>https://www.gaoxiaojob.com/announcement/detail/381907.html</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -2572,27 +2617,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ShanghaiTech</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>创业与管理学院</t>
+          <t>经济管理学院</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>上海科技大学创业与管理学院诚聘英才</t>
+          <t>清华大学经济管理学院博士后招聘</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>招满即止</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2602,12 +2647,17 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://sem.shanghaitech.edu.cn/2026/0922/c3517a1127559/page.htm</t>
+          <t>https://sem.tsinghua.edu.cn/js/bshldz/bshzp.htm</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>postdoc@sem.tsinghua.edu.cn</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -2619,27 +2669,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tongji University</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>经济与管理学院</t>
+          <t>经济管理学院</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Job Posting: Join Tongji SEM Prestigious Research Faculty</t>
+          <t>清华大学经济管理学院应用经济学流动站（合作导师董丰）2026年招聘博士后</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>截止日期2026-12-31</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2649,12 +2699,17 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://sem.tongji.edu.cn/semch/56204.html</t>
+          <t>https://www.gaoxiaojob.com/announcement/detail/395746.html</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>postdoc@sem.tsinghua.edu.cn</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -2666,40 +2721,6792 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>清华大学经济管理学院教师招聘（2026年10月更新）</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>常年招聘</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sem.tsinghua.edu.cn/js/jszp.htm</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>scholar@sem.tsinghua.edu.cn</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UIBE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>中国金融学院</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>中国金融学院2026年专职教师招聘公告</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://sbf.uibe.edu.cn/tzgg/b20abafc23f940349876baa87054aace.htm</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>UIBE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>国际经济贸易学院</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>对外经济贸易大学2026年度事业编专职教学科研人员、师资博士后招聘公告</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>含国际经济贸易学院等经管岗位</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>https://hr.uibe.edu.cn/jszp/zpxx/654c850954d7459abbde78b5ebc62820.htm</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>UIBE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>国际经济贸易学院/中国金融学院/经济学院</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>对外经济贸易大学全球价值链研究院专职教学科研人员招聘相关公告</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://hr.uibe.edu.cn/jszp/zpxx/ed338932d6d94149945898e2ab2429c7.htm</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>UIBE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>全球创新与治理研究院</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>对外经济贸易大学全球创新与治理研究院2025年专职教学科研人员招聘公告</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>产业经济学方向</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>https://agig.uibe.edu.cn/tzgg/e30c29f3c079417eadaaedb5f16dfc54.htm</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>USTB</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>北京科技大学经济管理学院博士后招聘</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>含经济学、金融学等领域</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.ustb.edu.cn/szll/bshldz/bshzp/index.htm</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>jgzp@ustb.edu.cn</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>USTB</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>经济管理学院2025年诚聘海内外英才</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>常年招聘教师/博士后</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.ustb.edu.cn/xwzx/tzgg/a2ffc3d9c3d9495baeba6c87e507644c.htm</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>jgzp@ustb.edu.cn</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>USTB</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>经济管理学院2025年诚聘海内外英才（人才招聘栏目）</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>常年招聘</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.ustb.edu.cn/rczp/a2ffc3d9c3d9495baeba6c87e507644c.htm</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>jgzp@ustb.edu.cn</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>USTB</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>经济管理学院诚聘海内外英才（师资队伍招聘页）</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>常年招聘</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.ustb.edu.cn/szll/jszp/index.htm</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>jgzp@ustb.edu.cn</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Nankai University</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>金融学院</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026年南开大学青年学科带头人岗位岗位招聘公告（金融学院）</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://finance.nankai.edu.cn/2026/0119/c34541a589287/page.htm</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Nankai University</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>南开大学商学院诚聘全球英才</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://nbr.nankai.edu.cn/nkglpl/news/view/20251106121718001</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Nankai University</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>南开大学经济学院2026年人才引进、教职工公开招聘、博士后招收公告</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://economics.nankai.edu.cn/2025/1211/c16001a586532/page.htm</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Nankai University</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>南开大学经济学院2026年教学科研人员招聘启事</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://economics.nankai.edu.cn/2025/1120/c16001a584393/page.htm</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Nankai University</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>金融学院</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>金融学院2026年教学科研（副高）岗位招聘公告</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://finance.nankai.edu.cn/2025/1219/c34541a587299/page.htm</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tianjin Normal University</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026年天津师范大学第一批招聘（博士层次专业技术岗位）公告</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>http://www.jiaoshizhaopin.net/tianjin/jobshow_511040.html</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tianjin Normal University</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>天津师范大学数量经济学经济学院教师岗招聘</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencehr.net/job/208814.html</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Tianjin University</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>管理与经济学部</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>天津大学管理与经济学部2026年诚邀英才依托申报海外优青项目</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gxszw.com/region/tianjin/gxzptj/202601/30123168.html</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HEBUT</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>河北工业大学2026年公开选聘工作人员公告（专任教师）</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hebut.edu.cn/rczp/zpgg/be54ac68d1e34c1ab0f57e8afdfc9c8f.htm</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HUEB</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>人力资源处</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>河北经贸大学2026年公开选聘工作人员公告（第一批）</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.hueb.edu.cn/info/1068/4413.htm</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hebei Finance University</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>金融学院</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>河北金融学院2026年公开选聘工作人员公告</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boshijob.com/article/202606/24284866.html</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Hebei University</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>人事处</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>河北大学2026年公开选聘工作人员公告</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.hbu.cn/info/1017/2038.htm</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Hebei University</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>河北大学经济学院相关招聘</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.hbu.edu.cn/info/1084/1669.htm</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>NCEPU Baoding</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>经济管理系</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>华北电力大学2026年度教学科研岗位招聘启事（经管学院转载）</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>https://business.ncepu.edu.cn/szll2/rczp/9ab45767dd944af290b7e2d4c0b41184.htm</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Shijiazhuang Tiedao University</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>石家庄铁道大学2026年公开选聘14名工作人员公告</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://460.net.cn/a/522403.html</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Yanshan University</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>燕山大学2026年公开选聘专任教师公告</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>http://jrzhufu.com/zhaopin/article/2269.html</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Yanshan University</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>燕山大学经济学专任教师招聘</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencehr.net/job/229026.html</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DMU</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>党委人才工作办公室</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>大连海事大学2026年度专任教师（博士）招聘公告</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://rcb.dlmu.edu.cn/info/1013/4752.htm</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DUFE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>管理科学与工程学院</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>东北财经大学管理科学与工程学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://smse.dufe.edu.cn/content_98151.html</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DUFE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>东北财经大学经济学院诚聘天下英才</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://econ.dufe.edu.cn/content_95758.html</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DUFE</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>财政税务学院</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>东北财经大学财政税务学院诚聘海内外英才</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://cs.dufe.edu.cn/content_96670.html</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DUT</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学2026年全球人才招聘</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://perdep.dlut.edu.cn/info/1401/21541.htm</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DUT</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>工商管理</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学2026年博士后招聘公告</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://perdep.dlut.edu.cn/info/1401/21561.htm</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DUT</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学盘锦校区2026年专任教师招聘公告</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://panjin.dlut.edu.cn/info/1342/48784.htm</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DUT</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学经济管理学院诚聘海内外优秀人才</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>http://sem.dlut.edu.cn/info/1072/7620.htm</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Liaoning University</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>辽宁大学商学院2026年面向社会公开招聘3名高层次和急需紧缺人才公告（第二批）</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gaoxiaojob.com/announcement/detail/424265.html</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Liaoning University</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>辽宁大学商学院2026年高层次人才招聘公告（第二批）</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://coba.lnu.edu.cn/info/1164/4976.htm</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>工商管理学院</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>东北大学2025年专任教师招聘启事</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.neu.edu.cn/2025/0623/c3973a288430/page.htm</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Donghua University</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>旭日工商管理学院</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>东华大学旭日工商管理学院研究助理教授（RAP）招聘公告</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://glxy.dhu.edu.cn/2026/0520/c20103a376231/page.htm</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Donghua University</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>旭日工商管理学院</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>东华大学旭日工商管理学院诚聘海内外英才</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>https://glxy.dhu.edu.cn/2024/1014/c20103a352033/page.htm</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Donghua University</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>旭日工商管理学院</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>东华大学旭日工商管理学院诚聘海内外高层次人才</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://glxy.dhu.edu.cn/2026/0520/c20103a376232/page.htm</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ECNU</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>中国自贸战略研究院/经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学中国自贸战略研究院博士后研究员招聘启事（长期有效）</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.ecnu.edu.cn/42/d7/c42845a738007/page.htm</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>rczp@sem.ecnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ECNU</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>中国自贸战略研究院/经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学中国自贸战略研究院招聘启事（长期有效）</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.ecnu.edu.cn/42/d8/c42845a738008/page.htm</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>hyshen@sem.ecnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ECUST</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>华东理工大学陈万思教授团队招聘博士后启事</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>https://bs.ecust.edu.cn/cms/ecust/szyky/szdw/zpqs.html</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ECUST</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>商学院管理科学与工程博士后科研流动站招聘启事</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://bs.ecust.edu.cn/cms/ecust/facultyAndResearch/teacherRecruit/450106463682564.html</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Fudan University</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>【2026年】复旦大学经济学院面向全球诚聘英才，热岑欢迎您的加盟</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>https://econ.fudan.edu.cn/info/1134/46327.htm</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>中银科技金融学院</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>上海交通大学中银科技金融学院诚聘天下英才</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97786.html</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/会计系</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>会计系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97769.html</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/信息技术与创新系</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>信息、技术与创新系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97772.html</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/数据与商务智能系</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>数据与商务智能系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97770.html</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>海外优青 | 欢迎依托上海交大安泰经济与管理学院申报</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/94461.html</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/管理科学系</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>管理科学系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97783.html</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/组织管理系</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>组织管理系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97785.html</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/经济系</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>经济系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97812.html</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SJTU</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>安泰经济与管理学院/金融系</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>金融系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97771.html</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SUFE</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026上海财经大学商学院世界经济与贸易系、产业经济系师资招聘</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>https://cob.sufe.edu.cn/Home/Detail/26953</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SUFE</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>统计与数据科学学院</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>上海财经大学统计与数据科学学院面向全球诚聘英才（Faculty Recruitment，2026）</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://ibdr.sufe.edu.cn/e0/17/c19471a253975/page.htm</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>recruit.ssm@mail.shufe.edu.cn</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SUFE</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>金融学院</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>上海财经大学金融学院2026年“毓秀人才计划”招聘启事</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>https://sof.sufe.edu.cn/d1/50/c7791a250192/page.htm</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>wangyachun@mail.shufe.edu.cn</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SUIBE</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>国际组织学院</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>上海对外经贸大学国际组织学院（贸易谈判学院）2026年诚聘海内外英才</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.suibe.edu.cn/gjzz/2025/0421/c21874a183262/page.htm</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SUIBE</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>人事处/人才招聘</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>上海对外经贸大学教学科研岗位人才招聘启事</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.suibe.edu.cn/rsc/2025/0401/c3652a182425/page.htm</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Shanghai University</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>上海大学经济学院2026年招聘1名数量经济学教师</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gaoxiaojob.com/announcement/detail/370987.html</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Shanghai University</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>经济学院数字经济与贸易教师岗位</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.shu.edu.cn/Ads/Ads?a=ff3d6c5d-27b3-4094-bb0c-f0ab7a5c945f</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ShanghaiTech</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>创业与管理学院</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Faculty Openings at ShanghaiTech SEM</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.shanghaitech.edu.cn/sem_en/2026/0922/c3708a1127557/page.htm</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>sem-recruit@shanghaitech.edu.cn</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ShanghaiTech</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>创业与管理学院</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>上海科技大学创业与管理学院诚聘英才</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.shanghaitech.edu.cn/2026/0922/c3517a1127559/page.htm</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ShanghaiTech</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>创业与管理学院</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>上海科技大学创业与管理学院诚聘英才（2026）</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://sem.shanghaitech.edu.cn/2026/0922/c3518a1127559/page.htm</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>sem-recruit@shanghaitech.edu.cn</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
         <is>
           <t>Tongji University</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>经济与管理学院</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>同济大学经济与管理学院应用经济博士后招聘</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>See announcement page</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Dept/HR</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>https://zp.tongji.edu.cn/info/1063/19717.htm</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Hohai University</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>河海大学商学院人才招聘公告（微信）</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://mp.weixin.qq.com/s/EjfNyNnvI_aeOxFolLR_2Q</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>无锡</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Jiangnan University</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>江南大学2026年人才招聘公告</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>http://renshi.jiangnan.edu.cn/info/1008/3329.htm</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>无锡</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Jiangnan University</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>江南大学2026年人才招聘公告（新闻网）</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://news.jiangnan.edu.cn/info/1132/106209.htm</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>镇江</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Jiangsu University</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>财经学院</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>江苏大学2026年公开招聘专任教师公告</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ujs.edu.cn/info/1093/211052.htm</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>NJUST</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>南京理工大学企业管理（经济管理学院-专任教师）</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencehr.net/job/228739.html</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>NJUST</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>南京理工大学会计学（经济管理学院-专任教师）</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.100zp.com/job/211061.html</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>NNU</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>南京师范大学商学院2026年公开招聘2名工作人员公告（第二批）</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gaoxiaojob.com/announcement/detail/426065.html</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Nanjing University</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>南京大学商学院2026年度研究系列人员招聘公告</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>https://nubs.nju.edu.cn/d9/7c/c17177a842108/page.htm</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Southeast University</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>IACMR 东南大学经济管理学院诚聘海内外英才</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>https://iacmr.org/%E6%8B%9B%E8%81%98%E4%BF%A1%E6%81%AF%EF%BD%9C%E4%B8%9C%E5%8D%97%E5%A4%A7%E5%AD%A6%E7%BB%8F%E6%B5%8E%E7%AE%A1%E7%90%86%E5%AD%A6%E9%99%A2%E8%AF%9A%E8%81%98%E6%B5%B7%E5%86%85%E5%A4%96%E8%8B%B1%E6%89%8D/</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Southeast University</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>东南大学经管学院诚聘海内外英才（2025长年有效）</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>https://em.seu.edu.cn/2025/0303/c34068a520025/page.htm</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>FAFU</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026????????????????????????/?????</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>????; ????/???/??????</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://rst.fujian.gov.cn/zw/ztzl/zxzt/sydwrczp/gccrczpfa/202605/t20260512_7146924.htm</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>FJNU</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>????????????????-??????</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencehr.net/job/227601.html</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>FJNU</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>协和学院</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>福建师范大学协和学院2026年高层次人才招聘公告</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://cuc.fjnu.edu.cn/2026/0518/c315a43167/page.htm</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>FJXU</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>??????2026????????????????/?????</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>????; ?????/????</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.fjjxu.edu.cn/2026/0402/c2784a119519/page.htm</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Fujian University of Technology</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>互联网经贸学院</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>福建理工大学2026年高层次人才招聘方案</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>招满即止</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://rst.fujian.gov.cn/zw/ztzl/zxzt/sydwrczp/gccrczpfa/202603/t20260330_7117134.htm</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Fuzhou University</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026?????????????????????????</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>????; ????????</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.fzu.edu.cn/info/1071/2641.htm</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Fuzhou University</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>????2026??????????????????</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://jgxy.fzu.edu.cn/info/1127/24608.htm</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Fuzhou University</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>????????????????????????</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>????; ????????</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.fzu.edu.cn/info/1071/2514.htm</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Fuzhou University of International Studies and Trade</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>国际商学院</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>福州外语外贸学院2026年优秀博士招聘公告</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fzfu.com/jsfzzx/info/1054/2245.htm</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>??/??</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Huaqiao University</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>???????????</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>????2026?????????????????</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hqu.edu.cn/info/1013/8005.htm</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Jimei University</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026??????????????????????/?????</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>????; ?????????</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://rst.fj.gov.cn/zw/ztzl/zxzt/sydwrczp/gccrczpfa/202602/t20260225_7100631.htm</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Jimei University</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>??????????????-????????</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencehr.net/job/211533.html</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Minjiang University</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>闽江大学计算机与大数据学院诚邀英才（参考校级方案）</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>campus scheme page; may lack econ</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://jsj.mju.edu.cn/2026/0529/c6083a219243/page.htm</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>莆田</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Putian University</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>2026年莆田学院公开招聘博士高层次人才方案</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>招满即止</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ptu.edu.cn/info/1024/26914.htm</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Quanzhou Normal University</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>2026?????????????????????????????</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qztc.edu.cn/2026/0804/c2094a294909/page.htm</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Xiamen University</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>?????/????????</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>????2026????????</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>https://postdoctor.xmu.edu.cn/info/1061/4196.htm</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Xiamen University</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>????????</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>????????????2025???????????????</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>?????/???; ??</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gxszw.com/region/fujian/gxzpfj/202508/19118908.html</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Xiamen University</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>????/WISE</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>?????????????????2026-2027??????????????????</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gaoxiaojob.com/announcement/detail/436031.html</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Xiamen University</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>经济学院/WISE</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>厦门大学WISE/经济学院2026-2027年诚聘海外研究人员（英才网）</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>http://www.gaoxiaozp.com/fujian/62361.html</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>佛山</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Foshan University</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>经济贸易学院</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>佛山大学数字经济【经济贸易学院-高层次人才】招聘</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>招满为止; 数字经济</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencehr.net/job/193240.html</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>GDUF</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>大数据与人工智能学院（金融统计）</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>【百万英才汇南粤】广东金融学院2026年大数据与人工智能学院诚聘师资公告</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>含金融统计与风险管理</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>https://ai.gduf.edu.cn/info/1099/1240.htm</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>gdufrczp@gduf.edu.cn</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>GDUT</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>广东工业大学经济学院高层次人才招聘</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>青百计划教师岗</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>https://jjxy.gdut.edu.cn/info/1055/3235.htm</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>jjrczhp@gdut.edu.cn</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>GDUT</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>百万英才汇南粤--广东工业大学高层次人才招聘简章（经济学院）</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>含经济学院博士后与青百</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>https://hr.gdut.edu.cn/info/1073/1195.htm</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>jjrczhp@gdut.edu.cn</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Guangdong University of Finance and Economics</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>“百万英才汇南粤”广东财经大学2026年博士后招聘公告</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>http://rsc.gdufe.edu.cn/2026/0306/c4710a233784/page.htm</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Guangdong University of Finance and Economics</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>大学人事处（含经济学博士后）</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>广东财经大学2026年招聘博士后（经济学/管理学/法学等）</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>常年诚聘; 含经济学</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>http://rsc.gdufe.edu.cn/2026/0429/c4948a238378/page.htm</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Guangdong University of Finance and Economics</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>广东财经大学面向海内外招聘学科方向带头人的公告</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>http://rsc.gdufe.edu.cn/2025/0116/c12800a215856/page.htm</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Guangdong University of Foreign Studies</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>人事处/人才招聘</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>广东外语外贸大学2026年招聘师资博士后研究...</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.gdufs.edu.cn/info/1083/12549.htm</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Guangdong University of Foreign Studies</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>人事处/人才招聘</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>广东外语外贸大学应用经济学博士后科研流动站2024年科研博士后研究人员招聘简章</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.gdufs.edu.cn/info/1083/11977.htm</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Guangdong University of Foreign Studies</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>人事处/人才招聘</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>广东外语外贸大学应用经济学博士后科研流动站2025年科研博士后研究人员招聘简章</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.gdufs.edu.cn/info/1083/12041.htm</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Guangdong University of Foreign Studies</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>人事处/人才招聘</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>广东外语外贸大学应用经济学博士后科研流动站2026年科研博士后研究人员招聘简章</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.gdufs.edu.cn/info/1083/12519.htm</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Guangdong University of Foreign Studies</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>人力资源部/经济贸易学院等</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>广外2026年招聘师资博士后（含应用经济学、金融学）</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>常年接受师资博士后申请</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>HR/学院</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.gdufs.edu.cn/info/1017/12559.htm</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Guangdong University of Foreign Studies</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>经济贸易学院</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>广外2026年面向海内外招聘人才（经贸学院含国贸/产业/数字经济等）</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>见公告各学院联系人</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Email/学院</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.gdufs.edu.cn/info/1017/12399.htm</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Guangdong University of Foreign Studies</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>应用经济学博士后流动站</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>广外应用经济学博士后科研流动站2026年科研博士后招聘简章</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>gpszk@gdufs.edu.cn; 常年接受</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>HR/导师</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.gdufs.edu.cn/info/1017/12909.htm</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>gpszk@gdufs.edu.cn</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Guangzhou University</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>经济与统计学院</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>广州大学2026年高层次人才招聘公告</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026年度长期有效</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.gzhu.edu.cn/info/1016/8191.htm</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Guangzhou University</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>经济与统计学院</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>广州大学经济与统计学院（李正辉课题组）2026年诚聘博士后</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>金融统计与风险管理、宏观经济统计等</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gaoxiaojob.com/announcement/detail/388060.html</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Guangzhou University</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>经济与统计学院</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>广州大学经济与统计学院（李正辉课题组）2026年诚聘博士后</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>lizh@gzhu.edu.cn</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gxszw.com/region/guangdong/gxzpgd/202603/30124547.html</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>lizh@gzhu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Guangzhou University</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>经济与统计学院</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>百万英才汇南粤 广州大学2026年博士后招聘简章</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>常年有效; jjytjxy@163.com</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gzhu.edu.cn/info/1205/31377.htm</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>jjytjxy@163.com</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Guangzhou University of Chinese Medicine</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>公共卫生与管理学院</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>广州中医药大学2025-2026学年度学科博士后招收公告</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>全年接收进站申请</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gzucm.edu.cn/info/1461/114061.htm</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Guangzhou University of Chinese Medicine</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>人事部（经济与管理类）</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>广州中医药大学诚聘海内外英才（含经济与管理类）</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>杏林学者; 经济与管理类</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.gzucm.edu.cn/info/1003/4003.htm</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Jinan University</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>经济与社会研究院</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Job Openings IESR 2026</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>iesr@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>AEA/Email</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://iesr.jnu.edu.cn/2025/1021/c17720a844641/page.htm</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>iesr@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Jinan University</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>招聘通知｜暨南大学经济学院2025年诚聘海内外英才</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>ojjy@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.jnu.edu.cn/2024/1129/c24919a826585/page.htm</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>ojjy@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Jinan University</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>大学博士后流动站（含理论/应用经济学）</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>暨南大学2026年博士后全球招聘公告</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>全年常态化接收</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://hrdam.jnu.edu.cn/2026/0413/c264a853500/page.htm</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Jinan University</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>大学博士后流动站（含理论/应用经济学）</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>暨南大学2026年博士后全球招聘（含应用经济学、理论经济学）</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>全年常态化接收</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>HR/导师</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://hrdam.jnu.edu.cn/2026/0413/c343a853500/page.htm</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Jinan University</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>经济与社会研究院</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>暨南大学冯帅章教授团队招聘博士后</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>材料发 iesr@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://iesr.jnu.edu.cn/2025/0624/c17209a839104/page.htm</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>iesr@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Jinan University</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>暨南大学经济学院2025年诚聘海内外英才（含教师各层次与博士后）</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>材料发 ojjy@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.jnu.edu.cn/2024/1129/c42192a826585/page.htm</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>ojjy@jnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SCAU</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>华南农业大学经济管理学院姜百臣教授研究团队招聘博士后启事</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>紫荆/全职博士后</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://cem.scau.edu.cn/2025/0221/c9875a399607/page.htm</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SCAU</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>华南农业大学经济管理学院易法敏教授研究团队招聘博士后</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>理论/应用经济学/数字经济/金融学</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://cem.scau.edu.cn/2025/0221/c9875a399618/page.htm</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SCAU</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>华南农业大学经济管理学院杨学儒教授研究团队招聘博士后启事</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>紫荆/全职博士后</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://cem.scau.edu.cn/2025/0221/c9875a399608/page.htm</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>SCAU</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>华南农业大学经济管理学院柳松教授研究团队招聘博士后启事</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>紫荆/全职博士后</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://cem.scau.edu.cn/2025/0221/c9875a399594/page.htm</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>SCAU</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>经济管理学院</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>华南农业大学经济管理学院段伟教授研究团队招聘博士后启事</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>紫荆/全职博士后</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://cem.scau.edu.cn/2025/0221/c9875a399586/page.htm</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SCNU</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>华南师范大学2025年公开招聘教学科研人员公告</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>见岗位表</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>http://em.scnu.edu.cn/a/20250910/10765.html</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>汕头</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Shantou University</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>汕头大学商学院博士后招聘（数字经济/宏观经济/产业经济）</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>全年接受入站申请</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>https://biz.stu.edu.cn/gk/cpyc/bshzp.htm</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>biz_recruitment@stu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>汕头</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Shantou University</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>汕头大学商学院教师招聘（含应用经济学/数字经济）</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>biz_recruitment@stu.edu.cn</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Online/Email</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://biz.stu.edu.cn/gk/cpyc/jszp.htm</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>biz_recruitment@stu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>South China Normal University</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>华南师范大学经济与管理学院博士后流动站常年招收（理论/应用经济学）</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>scnujgzp@126.com; 常年招收</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>http://em.scnu.edu.cn/xueshukeyan/boshihouliudongzhan/</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>scnujgzp@126.com</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>国际金融学院</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>中山大学国际金融学院诚聘海内外英才（教师+博士后）</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>常年有效; 应用经济学等</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>https://isbf.sysu.edu.cn/zh-hans/article/2827</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>广州/深圳</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>岭南学院</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>中山大学岭南学院2026年招聘教师（含教研岗与博士后）</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>CV to sunyxi@mail.sysu.edu.cn; rolling</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gaoxiaojob.com/announcement/detail/434822.html</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>sunyxi@mail.sysu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>GXUFE</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>广西财经学院2026年招聘高层次人才公告</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gaoxiaojob.com/announcement/detail/409543.html</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Guangxi Minzu University</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>广西民族大学2026年度公开招聘专任教师公告</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>https://rsc.gxmzu.edu.cn/info/1296/10555.htm</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Guangxi University</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>工商管理学院</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>广西大学海内外人才招聘（含工商管理学院）</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gxu.edu.cn/info/1364/34798.htm</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Guangxi University</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>广西大学经济学院诚聘海内外英才公告</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>https://sef.gxu.edu.cn/info/10836/90824.htm</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Hainan Normal University</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>人事处</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>海南师范大学2026年公开招聘专任教师公告</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hainnu.edu.cn/2026/0803/c499a168635/page.htm</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Hainan Normal University</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>经济与管理学院</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>海南师范大学经济与管理学院2026年高层次人才招聘启事</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>https://jgxy.hainnu.edu.cn/2026/1014/c352a170265/page.htm</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Hainan University</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>经济学科</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>拥抱自贸港，拥有未来｜海南大学经济学科诚聘海内外高层次人才</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>http://www.efnchina.com/info/1111/59241.htm</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Hainan University</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>国际商学院</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>海南大学2026年全职博士后招收公告</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>https://hro.hainanu.edu.cn/info/1223/9743.htm</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Hainan University</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>国际商学院</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>海南大学2026年招聘教学科研专业技术人员公告</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>https://hro.hainanu.edu.cn/info/1009/9413.htm</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Hainan University</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>国际商学院</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>海南大学2026年招聘教学科研专业技术人员公告（副本）</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>https://hro.hainanu.edu.cn/info/1074/9473.htm</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Hainan University</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>国际商学院</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>海南大学诚邀全球英才依托申报2026年海外优青项目</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>See announcement page</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Dept/HR</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>https://hro.hainanu.edu.cn/info/1074/9483.htm</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
         <is>
           <t>Postdoc</t>
         </is>
@@ -2799,6 +9606,288 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId374"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
